--- a/forecast/data/results_12.xlsx
+++ b/forecast/data/results_12.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{99DB7E86-9BD9-4D24-802C-E5BCD8ABF301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CC116C3-6628-4F15-8CB7-8BD2B32D87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1128" yWindow="336" windowWidth="20388" windowHeight="13644" xr2:uid="{54C55650-2207-4721-B44D-D6B7839F5217}"/>
+    <workbookView xWindow="1230" yWindow="270" windowWidth="15300" windowHeight="9960" xr2:uid="{F88E971C-6354-4E44-8263-82A7DCD4B89A}"/>
   </bookViews>
   <sheets>
     <sheet name="results_12" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>name</t>
   </si>
@@ -177,22 +172,91 @@
     <t>Q23680</t>
   </si>
   <si>
+    <t>N2701</t>
+  </si>
+  <si>
+    <t>N2737</t>
+  </si>
+  <si>
+    <t>N2743</t>
+  </si>
+  <si>
+    <t>N2688</t>
+  </si>
+  <si>
+    <t>N2721</t>
+  </si>
+  <si>
+    <t>N2841</t>
+  </si>
+  <si>
+    <t>N2554</t>
+  </si>
+  <si>
+    <t>N2615</t>
+  </si>
+  <si>
+    <t>N2522</t>
+  </si>
+  <si>
+    <t>N2544</t>
+  </si>
+  <si>
+    <t>N2208</t>
+  </si>
+  <si>
+    <t>N2186</t>
+  </si>
+  <si>
+    <t>N1979</t>
+  </si>
+  <si>
+    <t>N2130</t>
+  </si>
+  <si>
+    <t>N2144</t>
+  </si>
+  <si>
+    <t>N2465</t>
+  </si>
+  <si>
+    <t>N2511</t>
+  </si>
+  <si>
+    <t>N2257</t>
+  </si>
+  <si>
+    <t>N2355</t>
+  </si>
+  <si>
+    <t>N2373</t>
+  </si>
+  <si>
+    <t>N1861</t>
+  </si>
+  <si>
+    <t>N1747</t>
+  </si>
+  <si>
+    <t>N1790</t>
+  </si>
+  <si>
+    <t>N1789</t>
+  </si>
+  <si>
+    <t>N1751</t>
+  </si>
+  <si>
+    <t>N2780</t>
+  </si>
+  <si>
+    <t>N2783</t>
+  </si>
+  <si>
     <t>avg</t>
   </si>
   <si>
-    <t>median</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>Th</t>
-  </si>
-  <si>
-    <t>HW</t>
-  </si>
-  <si>
-    <t>RF</t>
+    <t>average</t>
   </si>
 </sst>
 </file>
@@ -201,14 +265,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -246,28 +310,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -275,7 +339,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -283,14 +347,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -298,14 +362,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -313,7 +377,7 @@
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -321,14 +385,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1062,31 +1126,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC43673-039B-4D53-8098-59538FBA49D7}">
-  <dimension ref="A1:T35"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5253919-043D-4941-80FA-5BD2C3713B39}">
+  <dimension ref="A2:T65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="8.796875" style="1"/>
-    <col min="9" max="9" width="8.796875" style="1"/>
-    <col min="13" max="13" width="8.796875" style="1"/>
-    <col min="17" max="17" width="8.796875" style="1"/>
+    <col min="5" max="5" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="1"/>
+    <col min="13" max="13" width="9.140625" style="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="F1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1165,52 +1215,52 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>0.18360754100000001</v>
+        <v>0.18360754063356599</v>
       </c>
       <c r="G3">
-        <v>0.15966381299999999</v>
+        <v>0.15966381270021099</v>
       </c>
       <c r="H3">
-        <v>-0.13040710599999999</v>
+        <v>-0.130407105561858</v>
       </c>
       <c r="I3" s="1">
         <v>3</v>
       </c>
       <c r="J3">
-        <v>0.27941283900000002</v>
+        <v>0.27941283926194599</v>
       </c>
       <c r="K3">
-        <v>0.27130085900000001</v>
+        <v>0.27130085928359798</v>
       </c>
       <c r="L3">
-        <v>-2.9032237999999998E-2</v>
+        <v>-2.9032237744607201E-2</v>
       </c>
       <c r="M3" s="1">
         <v>3</v>
       </c>
       <c r="N3">
-        <v>0.17542624900000001</v>
+        <v>0.17542624862439499</v>
       </c>
       <c r="O3">
-        <v>0.180520292</v>
+        <v>0.1805202916991</v>
       </c>
       <c r="P3">
-        <v>2.9038089E-2</v>
+        <v>2.9038089309036098E-2</v>
       </c>
       <c r="Q3" s="1">
         <v>3</v>
       </c>
       <c r="R3">
-        <v>0.19587443199999999</v>
+        <v>0.19587443206844701</v>
       </c>
       <c r="S3">
-        <v>0.28857855399999999</v>
+        <v>0.28857855429208001</v>
       </c>
       <c r="T3">
-        <v>0.47328342600000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>0.47328342573694399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1227,52 +1277,52 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>3.6791877000000001E-2</v>
+        <v>3.6791876555828398E-2</v>
       </c>
       <c r="G4">
-        <v>4.1557988999999997E-2</v>
+        <v>4.1557988610444997E-2</v>
       </c>
       <c r="H4">
-        <v>0.12954251</v>
+        <v>0.12954251048826901</v>
       </c>
       <c r="I4" s="1">
         <v>2</v>
       </c>
       <c r="J4">
-        <v>3.8420590999999997E-2</v>
+        <v>3.8420591140617202E-2</v>
       </c>
       <c r="K4">
-        <v>5.0898974999999999E-2</v>
+        <v>5.0898974884095699E-2</v>
       </c>
       <c r="L4">
-        <v>0.32478375199999998</v>
+        <v>0.32478375196801001</v>
       </c>
       <c r="M4" s="1">
         <v>3</v>
       </c>
       <c r="N4">
-        <v>3.0149100000000002E-2</v>
+        <v>3.01491001316672E-2</v>
       </c>
       <c r="O4">
-        <v>3.0823215000000001E-2</v>
+        <v>3.08232145170638E-2</v>
       </c>
       <c r="P4">
-        <v>2.2359352999999998E-2</v>
+        <v>2.2359353428546998E-2</v>
       </c>
       <c r="Q4" s="1">
         <v>3</v>
       </c>
       <c r="R4">
-        <v>4.9762948000000001E-2</v>
+        <v>4.9762948260834501E-2</v>
       </c>
       <c r="S4">
-        <v>5.1165591000000003E-2</v>
+        <v>5.1165590740838499E-2</v>
       </c>
       <c r="T4">
-        <v>2.8186482999999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2.8186482694956799E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1289,52 +1339,52 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>8.6780048999999998E-2</v>
+        <v>8.6780049154380298E-2</v>
       </c>
       <c r="G5">
-        <v>7.7099348999999998E-2</v>
+        <v>7.7099348675065904E-2</v>
       </c>
       <c r="H5">
-        <v>-0.111554448</v>
+        <v>-0.111554447982537</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
       </c>
       <c r="J5">
-        <v>0.12284807</v>
+        <v>0.122848069989426</v>
       </c>
       <c r="K5">
-        <v>0.118986614</v>
+        <v>0.118986614110941</v>
       </c>
       <c r="L5">
-        <v>-3.1432776000000003E-2</v>
+        <v>-3.1432776101548897E-2</v>
       </c>
       <c r="M5" s="1">
         <v>4</v>
       </c>
       <c r="N5">
-        <v>8.0500978000000001E-2</v>
+        <v>8.0500978249661806E-2</v>
       </c>
       <c r="O5">
-        <v>8.5929968999999995E-2</v>
+        <v>8.5929969084192606E-2</v>
       </c>
       <c r="P5">
-        <v>6.7440059999999996E-2</v>
+        <v>6.7440060389000495E-2</v>
       </c>
       <c r="Q5" s="1">
         <v>3</v>
       </c>
       <c r="R5">
-        <v>9.4327241000000006E-2</v>
+        <v>9.4327240946658994E-2</v>
       </c>
       <c r="S5">
-        <v>9.9227187999999994E-2</v>
+        <v>9.9227187669380698E-2</v>
       </c>
       <c r="T5">
-        <v>5.1946252999999998E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>5.1946252996974203E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1351,52 +1401,52 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>7.3232678999999995E-2</v>
+        <v>7.3232679426855907E-2</v>
       </c>
       <c r="G6">
-        <v>7.4182463000000004E-2</v>
+        <v>7.4182462834923593E-2</v>
       </c>
       <c r="H6">
-        <v>1.2969392999999999E-2</v>
+        <v>1.2969393111122199E-2</v>
       </c>
       <c r="I6" s="1">
         <v>4</v>
       </c>
       <c r="J6">
-        <v>5.2510576000000003E-2</v>
+        <v>5.2510576453064402E-2</v>
       </c>
       <c r="K6">
-        <v>5.4865380999999998E-2</v>
+        <v>5.48653807262071E-2</v>
       </c>
       <c r="L6">
-        <v>4.4844381000000003E-2</v>
+        <v>4.4844380545841098E-2</v>
       </c>
       <c r="M6" s="1">
         <v>4</v>
       </c>
       <c r="N6">
-        <v>5.6951126999999997E-2</v>
+        <v>5.6951127009641403E-2</v>
       </c>
       <c r="O6">
-        <v>4.8971130000000002E-2</v>
+        <v>4.89711302263987E-2</v>
       </c>
       <c r="P6">
-        <v>-0.14012008500000001</v>
+        <v>-0.14012008545312399</v>
       </c>
       <c r="Q6" s="1">
         <v>3</v>
       </c>
       <c r="R6">
-        <v>7.6112447999999999E-2</v>
+        <v>7.6112448428959797E-2</v>
       </c>
       <c r="S6">
-        <v>7.9337147999999996E-2</v>
+        <v>7.9337148218791995E-2</v>
       </c>
       <c r="T6">
-        <v>4.2367573999999998E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4.2367573982881303E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1413,52 +1463,52 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>1.6226933999999998E-2</v>
+        <v>1.6226934191726199E-2</v>
       </c>
       <c r="G7">
-        <v>2.3651722E-2</v>
+        <v>2.3651722483407401E-2</v>
       </c>
       <c r="H7">
-        <v>0.457559524</v>
+        <v>0.45755952442741799</v>
       </c>
       <c r="I7" s="1">
         <v>4</v>
       </c>
       <c r="J7">
-        <v>6.7291537999999998E-2</v>
+        <v>6.7291538045810798E-2</v>
       </c>
       <c r="K7">
-        <v>4.2479383000000003E-2</v>
+        <v>4.24793833523954E-2</v>
       </c>
       <c r="L7">
-        <v>-0.36872622300000002</v>
+        <v>-0.36872622344467398</v>
       </c>
       <c r="M7" s="1">
         <v>4</v>
       </c>
       <c r="N7">
-        <v>1.4011020000000001E-2</v>
+        <v>1.4011019505358E-2</v>
       </c>
       <c r="O7">
-        <v>3.8520772000000002E-2</v>
+        <v>3.8520771554929598E-2</v>
       </c>
       <c r="P7">
-        <v>1.7493196719999999</v>
+        <v>1.7493196722906901</v>
       </c>
       <c r="Q7" s="1">
         <v>4</v>
       </c>
       <c r="R7">
-        <v>1.7145278999999999E-2</v>
+        <v>1.7145278936806101E-2</v>
       </c>
       <c r="S7">
-        <v>7.7420434999999996E-2</v>
+        <v>7.74204346364325E-2</v>
       </c>
       <c r="T7">
-        <v>3.5155541019999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3.51555410219849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1475,52 +1525,52 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>3.6666302999999997E-2</v>
+        <v>3.6666303237942198E-2</v>
       </c>
       <c r="G8">
-        <v>0.22563826200000001</v>
+        <v>0.22563826205476101</v>
       </c>
       <c r="H8">
-        <v>5.1538317779999998</v>
+        <v>5.1538317781998604</v>
       </c>
       <c r="I8" s="1">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>3.2359962999999999E-2</v>
+        <v>3.2359962778767799E-2</v>
       </c>
       <c r="K8">
-        <v>0.26485915700000001</v>
+        <v>0.26485915686622402</v>
       </c>
       <c r="L8">
-        <v>7.1847794040000004</v>
+        <v>7.1847794040110902</v>
       </c>
       <c r="M8" s="1">
         <v>3</v>
       </c>
       <c r="N8">
-        <v>3.2771554000000001E-2</v>
+        <v>3.2771553947331299E-2</v>
       </c>
       <c r="O8">
-        <v>6.8179059E-2</v>
+        <v>6.8179058837721601E-2</v>
       </c>
       <c r="P8">
-        <v>1.0804341150000001</v>
+        <v>1.0804341151260299</v>
       </c>
       <c r="Q8" s="1">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>0.102057866</v>
+        <v>0.10205786599144601</v>
       </c>
       <c r="S8">
-        <v>4.3748676E-2</v>
+        <v>4.3748675825106199E-2</v>
       </c>
       <c r="T8">
-        <v>-0.571334601</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-0.57133460120778101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1537,52 +1587,52 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>8.8552183000000007E-2</v>
+        <v>8.8552183331845197E-2</v>
       </c>
       <c r="G9">
-        <v>3.8376901999999997E-2</v>
+        <v>3.8376902277081001E-2</v>
       </c>
       <c r="H9">
-        <v>-0.566618226</v>
+        <v>-0.56661822630318004</v>
       </c>
       <c r="I9" s="1">
         <v>2</v>
       </c>
       <c r="J9">
-        <v>5.6573378000000001E-2</v>
+        <v>5.6573378294431702E-2</v>
       </c>
       <c r="K9">
-        <v>0.16051792400000001</v>
+        <v>0.160517923689945</v>
       </c>
       <c r="L9">
-        <v>1.8373402569999999</v>
+        <v>1.83734025665822</v>
       </c>
       <c r="M9" s="1">
         <v>3</v>
       </c>
       <c r="N9">
-        <v>6.8866461000000004E-2</v>
+        <v>6.8866461003045595E-2</v>
       </c>
       <c r="O9">
-        <v>4.9808160999999997E-2</v>
+        <v>4.9808160541140602E-2</v>
       </c>
       <c r="P9">
-        <v>-0.27674284700000001</v>
+        <v>-0.27674284672566701</v>
       </c>
       <c r="Q9" s="1">
         <v>2</v>
       </c>
       <c r="R9">
-        <v>3.1775128999999999E-2</v>
+        <v>3.1775129446652499E-2</v>
       </c>
       <c r="S9">
-        <v>3.1850858000000003E-2</v>
+        <v>3.1850858129023198E-2</v>
       </c>
       <c r="T9">
-        <v>2.3832689999999999E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2.3832690437275601E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1599,52 +1649,52 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>0.41441280200000002</v>
+        <v>0.41441280189166002</v>
       </c>
       <c r="G10">
-        <v>0.46110917899999998</v>
+        <v>0.46110917905870702</v>
       </c>
       <c r="H10">
-        <v>0.112680827</v>
+        <v>0.112680826832311</v>
       </c>
       <c r="I10" s="1">
         <v>3</v>
       </c>
       <c r="J10">
-        <v>0.20699556299999999</v>
+        <v>0.20699556273721401</v>
       </c>
       <c r="K10">
-        <v>0.217572759</v>
+        <v>0.21757275915857799</v>
       </c>
       <c r="L10">
-        <v>5.1098663000000002E-2</v>
+        <v>5.1098662606561797E-2</v>
       </c>
       <c r="M10" s="1">
         <v>3</v>
       </c>
       <c r="N10">
-        <v>0.40938567599999998</v>
+        <v>0.40938567636867101</v>
       </c>
       <c r="O10">
-        <v>0.40115576400000003</v>
+        <v>0.401155763792376</v>
       </c>
       <c r="P10">
-        <v>-2.0103078999999999E-2</v>
+        <v>-2.0103078957952901E-2</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>0.51460218899999999</v>
+        <v>0.51460218939279201</v>
       </c>
       <c r="S10">
-        <v>0.51460218899999999</v>
+        <v>0.51460218939279201</v>
       </c>
       <c r="T10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1661,52 +1711,52 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>1.8524203E-2</v>
+        <v>1.8524202847874101E-2</v>
       </c>
       <c r="G11">
-        <v>2.9712962999999998E-2</v>
+        <v>2.9712963068275099E-2</v>
       </c>
       <c r="H11">
-        <v>0.60400764900000004</v>
+        <v>0.60400764946735597</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
       </c>
       <c r="J11">
-        <v>1.5456228000000001E-2</v>
+        <v>1.54562278146207E-2</v>
       </c>
       <c r="K11">
-        <v>2.9280183000000001E-2</v>
+        <v>2.9280183219469E-2</v>
       </c>
       <c r="L11">
-        <v>0.89439387000000004</v>
+        <v>0.89439386962009104</v>
       </c>
       <c r="M11" s="1">
         <v>2</v>
       </c>
       <c r="N11">
-        <v>4.4065488999999999E-2</v>
+        <v>4.40654888919167E-2</v>
       </c>
       <c r="O11">
-        <v>2.1547225E-2</v>
+        <v>2.1547225048078801E-2</v>
       </c>
       <c r="P11">
-        <v>-0.51101813299999999</v>
+        <v>-0.51101813255880002</v>
       </c>
       <c r="Q11" s="1">
         <v>2</v>
       </c>
       <c r="R11">
-        <v>8.0177528999999997E-2</v>
+        <v>8.0177529097606601E-2</v>
       </c>
       <c r="S11">
-        <v>7.9363447000000004E-2</v>
+        <v>7.9363447037885906E-2</v>
       </c>
       <c r="T11">
-        <v>-1.0153494000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-1.0153493988691E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1723,52 +1773,52 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0.33039430199999997</v>
+        <v>0.33039430187593999</v>
       </c>
       <c r="G12">
-        <v>0.92519948100000005</v>
+        <v>0.92519948111737305</v>
       </c>
       <c r="H12">
-        <v>1.8002888539999999</v>
+        <v>1.8002888544511699</v>
       </c>
       <c r="I12" s="1">
         <v>3</v>
       </c>
       <c r="J12">
-        <v>9.9957230999999994E-2</v>
+        <v>9.9957230900450597E-2</v>
       </c>
       <c r="K12">
-        <v>9.5590511000000003E-2</v>
+        <v>9.5590510604052298E-2</v>
       </c>
       <c r="L12">
-        <v>-4.3685887E-2</v>
+        <v>-4.3685887024493601E-2</v>
       </c>
       <c r="M12" s="1">
         <v>2</v>
       </c>
       <c r="N12">
-        <v>0.10332149</v>
+        <v>0.103321489509923</v>
       </c>
       <c r="O12">
-        <v>0.112218162</v>
+        <v>0.112218161716636</v>
       </c>
       <c r="P12">
-        <v>8.6106696999999996E-2</v>
+        <v>8.6106697153826295E-2</v>
       </c>
       <c r="Q12" s="1">
         <v>3</v>
       </c>
       <c r="R12">
-        <v>5.9721771E-2</v>
+        <v>5.9721771033707002E-2</v>
       </c>
       <c r="S12">
-        <v>5.9354647000000003E-2</v>
+        <v>5.9354646714509997E-2</v>
       </c>
       <c r="T12">
-        <v>-6.1472439999999996E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-6.1472443439396099E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1785,52 +1835,52 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>4.5538083E-2</v>
+        <v>4.5538083411783198E-2</v>
       </c>
       <c r="G13">
-        <v>4.1014660000000001E-2</v>
+        <v>4.1014660410022101E-2</v>
       </c>
       <c r="H13">
-        <v>-9.9332748999999998E-2</v>
+        <v>-9.9332748830413903E-2</v>
       </c>
       <c r="I13" s="1">
         <v>3</v>
       </c>
       <c r="J13">
-        <v>6.4300776000000004E-2</v>
+        <v>6.4300776021400594E-2</v>
       </c>
       <c r="K13">
-        <v>6.5344444000000002E-2</v>
+        <v>6.5344444301052906E-2</v>
       </c>
       <c r="L13">
-        <v>1.6231037E-2</v>
+        <v>1.6231037076519399E-2</v>
       </c>
       <c r="M13" s="1">
         <v>4</v>
       </c>
       <c r="N13">
-        <v>4.4560503000000001E-2</v>
+        <v>4.45605030491018E-2</v>
       </c>
       <c r="O13">
-        <v>5.2854271000000001E-2</v>
+        <v>5.2854270505683698E-2</v>
       </c>
       <c r="P13">
-        <v>0.18612373900000001</v>
+        <v>0.186123739389632</v>
       </c>
       <c r="Q13" s="1">
         <v>3</v>
       </c>
       <c r="R13">
-        <v>4.3371194000000002E-2</v>
+        <v>4.3371193887583703E-2</v>
       </c>
       <c r="S13">
-        <v>4.2165520999999997E-2</v>
+        <v>4.2165521064128998E-2</v>
       </c>
       <c r="T13">
-        <v>-2.7798930999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-2.7798930935120199E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1847,52 +1897,52 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>0.13405107999999999</v>
+        <v>0.13405108032150301</v>
       </c>
       <c r="G14">
-        <v>0.17160761599999999</v>
+        <v>0.171607616323871</v>
       </c>
       <c r="H14">
-        <v>0.28016585900000002</v>
+        <v>0.28016585850925901</v>
       </c>
       <c r="I14" s="1">
         <v>7</v>
       </c>
       <c r="J14">
-        <v>0.142823009</v>
+        <v>0.142823009458759</v>
       </c>
       <c r="K14">
-        <v>0.14882105100000001</v>
+        <v>0.14882105110604599</v>
       </c>
       <c r="L14">
-        <v>4.1996326E-2</v>
+        <v>4.1996325872260001E-2</v>
       </c>
       <c r="M14" s="1">
         <v>5</v>
       </c>
       <c r="N14">
-        <v>0.16056363300000001</v>
+        <v>0.16056363346371</v>
       </c>
       <c r="O14">
-        <v>0.154646073</v>
+        <v>0.154646072751912</v>
       </c>
       <c r="P14">
-        <v>-3.6854924999999997E-2</v>
+        <v>-3.6854925266351098E-2</v>
       </c>
       <c r="Q14" s="1">
         <v>5</v>
       </c>
       <c r="R14">
-        <v>0.19038089799999999</v>
+        <v>0.19038089782214701</v>
       </c>
       <c r="S14">
-        <v>0.189352311</v>
+        <v>0.18935231090506699</v>
       </c>
       <c r="T14">
-        <v>-5.4027839999999999E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-5.4027842543352897E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1909,52 +1959,52 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>0.172619723</v>
+        <v>0.17261972260116301</v>
       </c>
       <c r="G15">
-        <v>0.17013653400000001</v>
+        <v>0.170136533995393</v>
       </c>
       <c r="H15">
-        <v>-1.4385312000000001E-2</v>
+        <v>-1.4385312224763899E-2</v>
       </c>
       <c r="I15" s="1">
         <v>2</v>
       </c>
       <c r="J15">
-        <v>0.205893469</v>
+        <v>0.205893468651591</v>
       </c>
       <c r="K15">
-        <v>0.219702904</v>
+        <v>0.21970290426081701</v>
       </c>
       <c r="L15">
-        <v>6.7070779999999997E-2</v>
+        <v>6.7070780339293395E-2</v>
       </c>
       <c r="M15" s="1">
         <v>3</v>
       </c>
       <c r="N15">
-        <v>0.19684426299999999</v>
+        <v>0.19684426285421</v>
       </c>
       <c r="O15">
-        <v>0.200088448</v>
+        <v>0.200088448094426</v>
       </c>
       <c r="P15">
-        <v>1.6480973999999999E-2</v>
+        <v>1.6480974315308299E-2</v>
       </c>
       <c r="Q15" s="1">
         <v>3</v>
       </c>
       <c r="R15">
-        <v>0.16865893500000001</v>
+        <v>0.168658935491909</v>
       </c>
       <c r="S15">
-        <v>0.16323258299999999</v>
+        <v>0.16323258264533599</v>
       </c>
       <c r="T15">
-        <v>-3.2173527E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-3.2173527188145902E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1971,52 +2021,52 @@
         <v>3</v>
       </c>
       <c r="F16">
-        <v>0.275976112</v>
+        <v>0.275976111998259</v>
       </c>
       <c r="G16">
-        <v>0.24688627199999999</v>
+        <v>0.24688627224322299</v>
       </c>
       <c r="H16">
-        <v>-0.10540709299999999</v>
+        <v>-0.10540709318790401</v>
       </c>
       <c r="I16" s="1">
         <v>2</v>
       </c>
       <c r="J16">
-        <v>0.15134118699999999</v>
+        <v>0.151341186674883</v>
       </c>
       <c r="K16">
-        <v>0.14892804500000001</v>
+        <v>0.148928044999079</v>
       </c>
       <c r="L16">
-        <v>-1.5945042999999999E-2</v>
+        <v>-1.5945042647166001E-2</v>
       </c>
       <c r="M16" s="1">
         <v>2</v>
       </c>
       <c r="N16">
-        <v>0.16171796999999999</v>
+        <v>0.16171797029138299</v>
       </c>
       <c r="O16">
-        <v>0.15620252000000001</v>
+        <v>0.15620252043232699</v>
       </c>
       <c r="P16">
-        <v>-3.4105362E-2</v>
+        <v>-3.4105361631231401E-2</v>
       </c>
       <c r="Q16" s="1">
         <v>3</v>
       </c>
       <c r="R16">
-        <v>0.21015119400000001</v>
+        <v>0.210151193608798</v>
       </c>
       <c r="S16">
-        <v>0.20692797299999999</v>
+        <v>0.206927973113676</v>
       </c>
       <c r="T16">
-        <v>-1.5337626E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-1.5337626400170499E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2033,52 +2083,52 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>0.150812272</v>
+        <v>0.15081227161192301</v>
       </c>
       <c r="G17">
-        <v>0.219773207</v>
+        <v>0.21977320714922799</v>
       </c>
       <c r="H17">
-        <v>0.457263423</v>
+        <v>0.457263422931246</v>
       </c>
       <c r="I17" s="1">
         <v>3</v>
       </c>
       <c r="J17">
-        <v>9.3037420999999995E-2</v>
+        <v>9.3037420529476597E-2</v>
       </c>
       <c r="K17">
-        <v>9.8525763000000002E-2</v>
+        <v>9.8525762787136095E-2</v>
       </c>
       <c r="L17">
-        <v>5.8990697000000002E-2</v>
+        <v>5.89906967156364E-2</v>
       </c>
       <c r="M17" s="1">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>0.105545977</v>
+        <v>0.105545977276075</v>
       </c>
       <c r="O17">
-        <v>0.12757067999999999</v>
+        <v>0.12757068049162901</v>
       </c>
       <c r="P17">
-        <v>0.20867401899999999</v>
+        <v>0.20867401850801601</v>
       </c>
       <c r="Q17" s="1">
         <v>2</v>
       </c>
       <c r="R17">
-        <v>0.18888754299999999</v>
+        <v>0.188887542676905</v>
       </c>
       <c r="S17">
-        <v>0.14937137</v>
+        <v>0.149371369668237</v>
       </c>
       <c r="T17">
-        <v>-0.20920475999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-0.20920475987270701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2095,52 +2145,52 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>0.110578783</v>
+        <v>0.110578783332342</v>
       </c>
       <c r="G18">
-        <v>6.4931622999999994E-2</v>
+        <v>6.4931622869492403E-2</v>
       </c>
       <c r="H18">
-        <v>-0.412802159</v>
+        <v>-0.412802158671421</v>
       </c>
       <c r="I18" s="1">
         <v>2</v>
       </c>
       <c r="J18">
-        <v>7.3271883999999995E-2</v>
+        <v>7.3271884424819703E-2</v>
       </c>
       <c r="K18">
-        <v>8.2027350999999998E-2</v>
+        <v>8.2027350995835094E-2</v>
       </c>
       <c r="L18">
-        <v>0.119492854</v>
+        <v>0.119492853769837</v>
       </c>
       <c r="M18" s="1">
         <v>2</v>
       </c>
       <c r="N18">
-        <v>8.4208931000000001E-2</v>
+        <v>8.4208930993360701E-2</v>
       </c>
       <c r="O18">
-        <v>9.1568855000000005E-2</v>
+        <v>9.1568855213266798E-2</v>
       </c>
       <c r="P18">
-        <v>8.7400755999999996E-2</v>
+        <v>8.7400755870969293E-2</v>
       </c>
       <c r="Q18" s="1">
         <v>2</v>
       </c>
       <c r="R18">
-        <v>8.3191714999999999E-2</v>
+        <v>8.3191714674297396E-2</v>
       </c>
       <c r="S18">
-        <v>7.7694498000000001E-2</v>
+        <v>7.7694498375169799E-2</v>
       </c>
       <c r="T18">
-        <v>-6.6078892E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-6.6078891637822199E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2157,22 +2207,22 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>2.1955993E-2</v>
+        <v>2.1955992943111499E-2</v>
       </c>
       <c r="G19">
-        <v>4.2226069999999997E-2</v>
+        <v>4.2226070165471703E-2</v>
       </c>
       <c r="H19">
-        <v>0.92321386999999999</v>
+        <v>0.92321387034876301</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>4.4326625000000001E-2</v>
+        <v>4.4326625084573502E-2</v>
       </c>
       <c r="K19">
-        <v>4.4326625000000001E-2</v>
+        <v>4.4326625084573502E-2</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2181,28 +2231,28 @@
         <v>3</v>
       </c>
       <c r="N19">
-        <v>0.102770416</v>
+        <v>0.10277041618836499</v>
       </c>
       <c r="O19">
-        <v>8.9746927000000004E-2</v>
+        <v>8.9746926530920104E-2</v>
       </c>
       <c r="P19">
-        <v>-0.126724111</v>
+        <v>-0.12672411128095901</v>
       </c>
       <c r="Q19" s="1">
         <v>2</v>
       </c>
       <c r="R19">
-        <v>0.13970151</v>
+        <v>0.13970150992602801</v>
       </c>
       <c r="S19">
-        <v>0.13836242700000001</v>
+        <v>0.138362426655607</v>
       </c>
       <c r="T19">
-        <v>-9.5853169999999994E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-9.5853170887709397E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -2219,52 +2269,52 @@
         <v>4</v>
       </c>
       <c r="F20">
-        <v>0.15653223199999999</v>
+        <v>0.156532231627065</v>
       </c>
       <c r="G20">
-        <v>8.1580101000000002E-2</v>
+        <v>8.1580100583596604E-2</v>
       </c>
       <c r="H20">
-        <v>-0.478828739</v>
+        <v>-0.47882873874845699</v>
       </c>
       <c r="I20" s="1">
         <v>4</v>
       </c>
       <c r="J20">
-        <v>0.239794698</v>
+        <v>0.23979469835471201</v>
       </c>
       <c r="K20">
-        <v>0.26392131299999999</v>
+        <v>0.263921312801776</v>
       </c>
       <c r="L20">
-        <v>0.100613627</v>
+        <v>0.100613627459666</v>
       </c>
       <c r="M20" s="1">
         <v>4</v>
       </c>
       <c r="N20">
-        <v>0.211664716</v>
+        <v>0.211664715776094</v>
       </c>
       <c r="O20">
-        <v>0.22150603099999999</v>
+        <v>0.22150603055877699</v>
       </c>
       <c r="P20">
-        <v>4.6494829000000001E-2</v>
+        <v>4.6494829081924198E-2</v>
       </c>
       <c r="Q20" s="1">
         <v>4</v>
       </c>
       <c r="R20">
-        <v>0.175054295</v>
+        <v>0.17505429547764401</v>
       </c>
       <c r="S20">
-        <v>0.18638845300000001</v>
+        <v>0.18638845306021601</v>
       </c>
       <c r="T20">
-        <v>6.4746526999999998E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6.4746526508515603E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -2281,52 +2331,52 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>0.14184759799999999</v>
+        <v>0.14184759775533801</v>
       </c>
       <c r="G21">
-        <v>0.138786824</v>
+        <v>0.13878682435547601</v>
       </c>
       <c r="H21">
-        <v>-2.1577901E-2</v>
+        <v>-2.1577900847792601E-2</v>
       </c>
       <c r="I21" s="1">
         <v>2</v>
       </c>
       <c r="J21">
-        <v>6.8547774000000006E-2</v>
+        <v>6.8547774383294804E-2</v>
       </c>
       <c r="K21">
-        <v>8.6225771000000007E-2</v>
+        <v>8.6225771425909495E-2</v>
       </c>
       <c r="L21">
-        <v>0.25789308599999999</v>
+        <v>0.25789308554010199</v>
       </c>
       <c r="M21" s="1">
         <v>2</v>
       </c>
       <c r="N21">
-        <v>9.2029286000000002E-2</v>
+        <v>9.2029285735425598E-2</v>
       </c>
       <c r="O21">
-        <v>7.9933414999999994E-2</v>
+        <v>7.9933414958884105E-2</v>
       </c>
       <c r="P21">
-        <v>-0.13143501699999999</v>
+        <v>-0.13143501744994299</v>
       </c>
       <c r="Q21" s="1">
         <v>2</v>
       </c>
       <c r="R21">
-        <v>0.130213199</v>
+        <v>0.13021319928339101</v>
       </c>
       <c r="S21">
-        <v>0.12693722800000001</v>
+        <v>0.12693722774902799</v>
       </c>
       <c r="T21">
-        <v>-2.5158521E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-2.5158521197481701E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2343,52 +2393,52 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>0.24452538300000001</v>
+        <v>0.24452538271348101</v>
       </c>
       <c r="G22">
-        <v>0.19791234899999999</v>
+        <v>0.197912348503858</v>
       </c>
       <c r="H22">
-        <v>-0.190626567</v>
+        <v>-0.19062656683065399</v>
       </c>
       <c r="I22" s="1">
         <v>4</v>
       </c>
       <c r="J22">
-        <v>0.24147954899999999</v>
+        <v>0.24147954906430999</v>
       </c>
       <c r="K22">
-        <v>0.32120598900000003</v>
+        <v>0.32120598904198799</v>
       </c>
       <c r="L22">
-        <v>0.33015814500000001</v>
+        <v>0.33015814501312302</v>
       </c>
       <c r="M22" s="1">
         <v>3</v>
       </c>
       <c r="N22">
-        <v>0.24077034999999999</v>
+        <v>0.24077035022764401</v>
       </c>
       <c r="O22">
-        <v>0.25232835799999997</v>
+        <v>0.25232835841780399</v>
       </c>
       <c r="P22">
-        <v>4.8004284000000001E-2</v>
+        <v>4.8004283663801398E-2</v>
       </c>
       <c r="Q22" s="1">
         <v>3</v>
       </c>
       <c r="R22">
-        <v>0.222765882</v>
+        <v>0.222765882151616</v>
       </c>
       <c r="S22">
-        <v>0.236197038</v>
+        <v>0.236197038486615</v>
       </c>
       <c r="T22">
-        <v>6.0292698999999998E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6.0292699246725097E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2405,52 +2455,52 @@
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0.222118337</v>
+        <v>0.222118337023573</v>
       </c>
       <c r="G23">
-        <v>0.158582627</v>
+        <v>0.15858262715093099</v>
       </c>
       <c r="H23">
-        <v>-0.286044415</v>
+        <v>-0.28604441544102899</v>
       </c>
       <c r="I23" s="1">
         <v>2</v>
       </c>
       <c r="J23">
-        <v>0.133200499</v>
+        <v>0.133200499011775</v>
       </c>
       <c r="K23">
-        <v>0.12400362400000001</v>
+        <v>0.12400362445026</v>
       </c>
       <c r="L23">
-        <v>-6.9045345999999994E-2</v>
+        <v>-6.9045346149204198E-2</v>
       </c>
       <c r="M23" s="1">
         <v>3</v>
       </c>
       <c r="N23">
-        <v>0.140013147</v>
+        <v>0.14001314677229601</v>
       </c>
       <c r="O23">
-        <v>0.149303775</v>
+        <v>0.14930377522014801</v>
       </c>
       <c r="P23">
-        <v>6.6355400999999994E-2</v>
+        <v>6.6355400632209002E-2</v>
       </c>
       <c r="Q23" s="1">
         <v>2</v>
       </c>
       <c r="R23">
-        <v>0.15146806800000001</v>
+        <v>0.15146806771427301</v>
       </c>
       <c r="S23">
-        <v>0.13731333800000001</v>
+        <v>0.13731333810260499</v>
       </c>
       <c r="T23">
-        <v>-9.3450254999999996E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-9.3450255392244996E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -2467,52 +2517,52 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>0.16293739199999999</v>
+        <v>0.16293739233656701</v>
       </c>
       <c r="G24">
-        <v>0.145080862</v>
+        <v>0.14508086239187001</v>
       </c>
       <c r="H24">
-        <v>-0.109591357</v>
+        <v>-0.109591357076663</v>
       </c>
       <c r="I24" s="1">
         <v>2</v>
       </c>
       <c r="J24">
-        <v>0.20480210700000001</v>
+        <v>0.20480210714470301</v>
       </c>
       <c r="K24">
-        <v>0.24472549499999999</v>
+        <v>0.24472549492634199</v>
       </c>
       <c r="L24">
-        <v>0.194936411</v>
+        <v>0.194936411242251</v>
       </c>
       <c r="M24" s="1">
         <v>2</v>
       </c>
       <c r="N24">
-        <v>0.17181469499999999</v>
+        <v>0.17181469519284401</v>
       </c>
       <c r="O24">
-        <v>0.19359705599999999</v>
+        <v>0.19359705605019101</v>
       </c>
       <c r="P24">
-        <v>0.126778218</v>
+        <v>0.12677821785207899</v>
       </c>
       <c r="Q24" s="1">
         <v>2</v>
       </c>
       <c r="R24">
-        <v>0.18242957000000001</v>
+        <v>0.182429569962508</v>
       </c>
       <c r="S24">
-        <v>0.19054641999999999</v>
+        <v>0.19054641988516</v>
       </c>
       <c r="T24">
-        <v>4.4493061E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4.4493060660726398E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -2529,10 +2579,10 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>5.1346712000000003E-2</v>
+        <v>5.1346711728193599E-2</v>
       </c>
       <c r="G25">
-        <v>5.1346712000000003E-2</v>
+        <v>5.1346711728193599E-2</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2541,10 +2591,10 @@
         <v>1</v>
       </c>
       <c r="J25">
-        <v>4.4943586000000001E-2</v>
+        <v>4.4943586159297E-2</v>
       </c>
       <c r="K25">
-        <v>4.4943586000000001E-2</v>
+        <v>4.4943586159297E-2</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2553,28 +2603,28 @@
         <v>3</v>
       </c>
       <c r="N25">
-        <v>6.9469385999999994E-2</v>
+        <v>6.9469386430741201E-2</v>
       </c>
       <c r="O25">
-        <v>7.6260069E-2</v>
+        <v>7.6260068828770095E-2</v>
       </c>
       <c r="P25">
-        <v>9.7750718E-2</v>
+        <v>9.7750717933848305E-2</v>
       </c>
       <c r="Q25" s="1">
         <v>2</v>
       </c>
       <c r="R25">
-        <v>0.108862586</v>
+        <v>0.108862585562559</v>
       </c>
       <c r="S25">
-        <v>0.113802556</v>
+        <v>0.113802556245182</v>
       </c>
       <c r="T25">
-        <v>4.5378039000000002E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4.5378039269370798E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2591,52 +2641,52 @@
         <v>5</v>
       </c>
       <c r="F26">
-        <v>0.21567476399999999</v>
+        <v>0.21567476396535401</v>
       </c>
       <c r="G26">
-        <v>0.28164250400000002</v>
+        <v>0.28164250417645098</v>
       </c>
       <c r="H26">
-        <v>0.30586675499999999</v>
+        <v>0.30586675510025502</v>
       </c>
       <c r="I26" s="1">
         <v>5</v>
       </c>
       <c r="J26">
-        <v>9.1211619999999993E-2</v>
+        <v>9.12116197000752E-2</v>
       </c>
       <c r="K26">
-        <v>0.115562737</v>
+        <v>0.115562737044775</v>
       </c>
       <c r="L26">
-        <v>0.26697385099999998</v>
+        <v>0.26697385075248597</v>
       </c>
       <c r="M26" s="1">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>0.156092487</v>
+        <v>0.15609248656833799</v>
       </c>
       <c r="O26">
-        <v>0.109953623</v>
+        <v>0.10995362316344801</v>
       </c>
       <c r="P26">
-        <v>-0.29558670300000001</v>
+        <v>-0.29558670259692299</v>
       </c>
       <c r="Q26" s="1">
         <v>4</v>
       </c>
       <c r="R26">
-        <v>0.208047855</v>
+        <v>0.208047855240798</v>
       </c>
       <c r="S26">
-        <v>0.196392495</v>
+        <v>0.196392495295936</v>
       </c>
       <c r="T26">
-        <v>-5.6022494999999999E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-5.6022495071492602E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -2653,52 +2703,52 @@
         <v>2</v>
       </c>
       <c r="F27">
-        <v>8.3387847000000001E-2</v>
+        <v>8.3387846935513196E-2</v>
       </c>
       <c r="G27">
-        <v>0.119695803</v>
+        <v>0.119695802964065</v>
       </c>
       <c r="H27">
-        <v>0.43541064299999999</v>
+        <v>0.43541064271188601</v>
       </c>
       <c r="I27" s="1">
         <v>2</v>
       </c>
       <c r="J27">
-        <v>0.152713825</v>
+        <v>0.15271382504946401</v>
       </c>
       <c r="K27">
-        <v>0.162742313</v>
+        <v>0.16274231343956899</v>
       </c>
       <c r="L27">
-        <v>6.5668504000000003E-2</v>
+        <v>6.5668503731451999E-2</v>
       </c>
       <c r="M27" s="1">
         <v>2</v>
       </c>
       <c r="N27">
-        <v>0.14174598099999999</v>
+        <v>0.14174598100060801</v>
       </c>
       <c r="O27">
-        <v>0.144333718</v>
+        <v>0.144333718004265</v>
       </c>
       <c r="P27">
-        <v>1.8256158000000001E-2</v>
+        <v>1.825615784934E-2</v>
       </c>
       <c r="Q27" s="1">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>0.20249510900000001</v>
+        <v>0.20249510928938899</v>
       </c>
       <c r="S27">
-        <v>0.20249510900000001</v>
+        <v>0.20249510928938899</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -2715,52 +2765,52 @@
         <v>2</v>
       </c>
       <c r="F28">
-        <v>0.17315045300000001</v>
+        <v>0.17315045250205</v>
       </c>
       <c r="G28">
-        <v>0.13712532399999999</v>
+        <v>0.137125324217485</v>
       </c>
       <c r="H28">
-        <v>-0.20805679499999999</v>
+        <v>-0.208056795486216</v>
       </c>
       <c r="I28" s="1">
         <v>2</v>
       </c>
       <c r="J28">
-        <v>0.147275406</v>
+        <v>0.147275406288324</v>
       </c>
       <c r="K28">
-        <v>8.2219241999999998E-2</v>
+        <v>8.22192417768004E-2</v>
       </c>
       <c r="L28">
-        <v>-0.44173135299999999</v>
+        <v>-0.44173135319119</v>
       </c>
       <c r="M28" s="1">
         <v>3</v>
       </c>
       <c r="N28">
-        <v>5.8267802E-2</v>
+        <v>5.8267802058530403E-2</v>
       </c>
       <c r="O28">
-        <v>3.4432537999999999E-2</v>
+        <v>3.4432537948088697E-2</v>
       </c>
       <c r="P28">
-        <v>-0.40906406699999998</v>
+        <v>-0.40906406743297102</v>
       </c>
       <c r="Q28" s="1">
         <v>3</v>
       </c>
       <c r="R28">
-        <v>5.7792647000000003E-2</v>
+        <v>5.7792647319186499E-2</v>
       </c>
       <c r="S28">
-        <v>5.2994551000000001E-2</v>
+        <v>5.2994551251880601E-2</v>
       </c>
       <c r="T28">
-        <v>-8.3022604E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-8.3022603910255094E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2777,52 +2827,52 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>7.9317635999999997E-2</v>
+        <v>7.9317635659424304E-2</v>
       </c>
       <c r="G29">
-        <v>3.5025220000000003E-2</v>
+        <v>3.5025219800764902E-2</v>
       </c>
       <c r="H29">
-        <v>-0.55841825700000003</v>
+        <v>-0.55841825705500203</v>
       </c>
       <c r="I29" s="1">
         <v>2</v>
       </c>
       <c r="J29">
-        <v>6.0266683000000001E-2</v>
+        <v>6.0266683013888302E-2</v>
       </c>
       <c r="K29">
-        <v>8.6295360000000002E-3</v>
+        <v>8.62953586370796E-3</v>
       </c>
       <c r="L29">
-        <v>-0.85681083800000002</v>
+        <v>-0.85681083756145504</v>
       </c>
       <c r="M29" s="1">
         <v>2</v>
       </c>
       <c r="N29">
-        <v>9.1467373000000005E-2</v>
+        <v>9.1467373306537397E-2</v>
       </c>
       <c r="O29">
-        <v>8.2199996999999997E-2</v>
+        <v>8.2199997131957095E-2</v>
       </c>
       <c r="P29">
-        <v>-0.101318928</v>
+        <v>-0.101318927608451</v>
       </c>
       <c r="Q29" s="1">
         <v>2</v>
       </c>
       <c r="R29">
-        <v>0.122141953</v>
+        <v>0.122141953364412</v>
       </c>
       <c r="S29">
-        <v>0.122438059</v>
+        <v>0.122438058940729</v>
       </c>
       <c r="T29">
-        <v>2.4242740000000001E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>2.42427411843388E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2839,52 +2889,52 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>0.10000807</v>
+        <v>0.100008069600291</v>
       </c>
       <c r="G30">
-        <v>0.130876621</v>
+        <v>0.13087662123069699</v>
       </c>
       <c r="H30">
-        <v>0.30866060899999997</v>
+        <v>0.30866060862667999</v>
       </c>
       <c r="I30" s="1">
         <v>6</v>
       </c>
       <c r="J30">
-        <v>2.5216723E-2</v>
+        <v>2.5216723215816101E-2</v>
       </c>
       <c r="K30">
-        <v>7.0171165999999993E-2</v>
+        <v>7.0171165680247199E-2</v>
       </c>
       <c r="L30">
-        <v>1.782723397</v>
+        <v>1.7827233966796801</v>
       </c>
       <c r="M30" s="1">
         <v>6</v>
       </c>
       <c r="N30">
-        <v>2.8026300000000001E-2</v>
+        <v>2.8026299667566101E-2</v>
       </c>
       <c r="O30">
-        <v>2.7218962999999999E-2</v>
+        <v>2.7218963477982298E-2</v>
       </c>
       <c r="P30">
-        <v>-2.8806378000000001E-2</v>
+        <v>-2.88063782646997E-2</v>
       </c>
       <c r="Q30" s="1">
         <v>5</v>
       </c>
       <c r="R30">
-        <v>2.1173661E-2</v>
+        <v>2.1173660561411799E-2</v>
       </c>
       <c r="S30">
-        <v>0.16776856700000001</v>
+        <v>0.16776856679206201</v>
       </c>
       <c r="T30">
-        <v>6.9234559520000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>6.9234559515804301</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2901,52 +2951,52 @@
         <v>3</v>
       </c>
       <c r="F31">
-        <v>0.17544100100000001</v>
+        <v>0.175441000714464</v>
       </c>
       <c r="G31">
-        <v>0.22129450000000001</v>
+        <v>0.22129449978768601</v>
       </c>
       <c r="H31">
-        <v>0.26136136300000001</v>
+        <v>0.261361363002311</v>
       </c>
       <c r="I31" s="1">
         <v>3</v>
       </c>
       <c r="J31">
-        <v>0.104466979</v>
+        <v>0.10446697887470099</v>
       </c>
       <c r="K31">
-        <v>0.104626206</v>
+        <v>0.104626205962213</v>
       </c>
       <c r="L31">
-        <v>1.5241860000000001E-3</v>
+        <v>1.52418581667737E-3</v>
       </c>
       <c r="M31" s="1">
         <v>3</v>
       </c>
       <c r="N31">
-        <v>0.118122329</v>
+        <v>0.118122329386497</v>
       </c>
       <c r="O31">
-        <v>0.119572954</v>
+        <v>0.119572953660546</v>
       </c>
       <c r="P31">
-        <v>1.2280694999999999E-2</v>
+        <v>1.228069478127E-2</v>
       </c>
       <c r="Q31" s="1">
         <v>3</v>
       </c>
       <c r="R31">
-        <v>0.123000897</v>
+        <v>0.123000897038183</v>
       </c>
       <c r="S31">
-        <v>0.12711973800000001</v>
+        <v>0.12711973826258</v>
       </c>
       <c r="T31">
-        <v>3.3486269999999999E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>3.3486269804346699E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -2963,83 +3013,1765 @@
         <v>4</v>
       </c>
       <c r="F32">
-        <v>0.115094473</v>
+        <v>0.115094473171249</v>
       </c>
       <c r="G32">
-        <v>3.2298622999999999E-2</v>
+        <v>3.2298623277332697E-2</v>
       </c>
       <c r="H32">
-        <v>-0.71937294299999999</v>
+        <v>-0.71937294304935295</v>
       </c>
       <c r="I32" s="1">
         <v>5</v>
       </c>
       <c r="J32">
-        <v>6.5027386000000006E-2</v>
+        <v>6.5027385535392404E-2</v>
       </c>
       <c r="K32">
-        <v>9.3046879999999998E-2</v>
+        <v>9.3046879657199405E-2</v>
       </c>
       <c r="L32">
-        <v>0.43088760100000001</v>
+        <v>0.430887600525732</v>
       </c>
       <c r="M32" s="1">
         <v>4</v>
       </c>
       <c r="N32">
-        <v>8.2461047999999995E-2</v>
+        <v>8.2461048235571405E-2</v>
       </c>
       <c r="O32">
-        <v>1.0359675E-2</v>
+        <v>1.03596753550548E-2</v>
       </c>
       <c r="P32">
-        <v>-0.87436886199999997</v>
+        <v>-0.87436886170231798</v>
       </c>
       <c r="Q32" s="1">
         <v>2</v>
       </c>
       <c r="R32">
-        <v>8.0548532000000006E-2</v>
+        <v>8.0548531697693604E-2</v>
       </c>
       <c r="S32">
-        <v>7.9215691000000005E-2</v>
+        <v>7.9215690939714506E-2</v>
       </c>
       <c r="T32">
-        <v>-1.6547052E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>-1.6547052191855701E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34">
+        <f>AVERAGE(H3:H32)</f>
+        <v>0.24099329969702213</v>
+      </c>
+      <c r="L34">
+        <f>AVERAGE(L3:L32)</f>
+        <v>0.40719970406933953</v>
+      </c>
+      <c r="P34">
+        <f>AVERAGE(P3:P32)</f>
+        <v>3.2101642688204542E-2</v>
+      </c>
+      <c r="T34">
+        <f>AVERAGE(T3:T32)</f>
+        <v>0.33535266077205689</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>50</v>
       </c>
-      <c r="H34">
-        <v>0.24099329999999999</v>
-      </c>
-      <c r="L34">
-        <v>0.407199704</v>
-      </c>
-      <c r="P34">
-        <v>3.2101642999999999E-2</v>
-      </c>
-      <c r="T34">
-        <v>0.335352661</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>135</v>
+      </c>
+      <c r="D37">
+        <v>4465</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>4.5975716329762301E-2</v>
+      </c>
+      <c r="G37">
+        <v>6.0762108041128103E-2</v>
+      </c>
+      <c r="H37">
+        <v>0.321613079507232</v>
+      </c>
+      <c r="I37" s="1">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>1.0039745354375299E-2</v>
+      </c>
+      <c r="K37">
+        <v>2.19685355298255E-2</v>
+      </c>
+      <c r="L37">
+        <v>1.1881566468467899</v>
+      </c>
+      <c r="M37" s="1">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <v>3.7405363137504997E-2</v>
+      </c>
+      <c r="O37">
+        <v>4.6173398969424101E-2</v>
+      </c>
+      <c r="P37">
+        <v>0.23440584708901299</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>6.3321785349017806E-2</v>
+      </c>
+      <c r="S37">
+        <v>6.3321785349017806E-2</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>51</v>
       </c>
-      <c r="H35">
-        <v>-7.1926560000000004E-3</v>
-      </c>
-      <c r="L35">
-        <v>5.5044679999999999E-2</v>
-      </c>
-      <c r="P35">
-        <v>1.7368565999999998E-2</v>
-      </c>
-      <c r="T35">
-        <v>-2.7013919999999999E-3</v>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="C38">
+        <v>134</v>
+      </c>
+      <c r="D38">
+        <v>4371</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>6.1141182673187897E-2</v>
+      </c>
+      <c r="G38">
+        <v>6.1141182673187897E-2</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>0.25039171769950502</v>
+      </c>
+      <c r="K38">
+        <v>0.188830726047817</v>
+      </c>
+      <c r="L38">
+        <v>-0.24585873773016401</v>
+      </c>
+      <c r="M38" s="1">
+        <v>3</v>
+      </c>
+      <c r="N38">
+        <v>4.71090804029521E-2</v>
+      </c>
+      <c r="O38">
+        <v>3.3211135161410499E-2</v>
+      </c>
+      <c r="P38">
+        <v>-0.29501627122975199</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>3</v>
+      </c>
+      <c r="R38">
+        <v>6.3423823889492303E-2</v>
+      </c>
+      <c r="S38">
+        <v>2.4569276504240602E-2</v>
+      </c>
+      <c r="T38">
+        <v>-0.612617546569734</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>134</v>
+      </c>
+      <c r="D39">
+        <v>4371</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>6.0615680070861801E-2</v>
+      </c>
+      <c r="G39">
+        <v>6.7819909329705899E-2</v>
+      </c>
+      <c r="H39">
+        <v>0.118850918614162</v>
+      </c>
+      <c r="I39" s="1">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>7.6771439116152002E-2</v>
+      </c>
+      <c r="K39">
+        <v>6.2534065773788602E-2</v>
+      </c>
+      <c r="L39">
+        <v>-0.18545143228099201</v>
+      </c>
+      <c r="M39" s="1">
+        <v>3</v>
+      </c>
+      <c r="N39">
+        <v>8.9795778949104593E-2</v>
+      </c>
+      <c r="O39">
+        <v>7.5752218812966496E-2</v>
+      </c>
+      <c r="P39">
+        <v>-0.156394435245089</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>3</v>
+      </c>
+      <c r="R39">
+        <v>0.12522190794202401</v>
+      </c>
+      <c r="S39">
+        <v>0.123242248426843</v>
+      </c>
+      <c r="T39">
+        <v>-1.5809210606316199E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>135</v>
+      </c>
+      <c r="D40">
+        <v>4465</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>0.105280733487791</v>
+      </c>
+      <c r="G40">
+        <v>0.118029079929651</v>
+      </c>
+      <c r="H40">
+        <v>0.121089073181073</v>
+      </c>
+      <c r="I40" s="1">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>0.149842899523249</v>
+      </c>
+      <c r="K40">
+        <v>4.5859514916966403E-2</v>
+      </c>
+      <c r="L40">
+        <v>-0.69394936254653095</v>
+      </c>
+      <c r="M40" s="1">
+        <v>3</v>
+      </c>
+      <c r="N40">
+        <v>0.14555455514150401</v>
+      </c>
+      <c r="O40">
+        <v>8.3227146476201205E-2</v>
+      </c>
+      <c r="P40">
+        <v>-0.4282065140779</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>0.140934980154755</v>
+      </c>
+      <c r="S40">
+        <v>0.168365196803482</v>
+      </c>
+      <c r="T40">
+        <v>0.19463029418677</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41">
+        <v>12</v>
+      </c>
+      <c r="C41">
+        <v>135</v>
+      </c>
+      <c r="D41">
+        <v>4465</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>3.71054584195121E-2</v>
+      </c>
+      <c r="G41">
+        <v>5.7595237488453098E-2</v>
+      </c>
+      <c r="H41">
+        <v>0.55220390588588597</v>
+      </c>
+      <c r="I41" s="1">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>2.51779559261355E-2</v>
+      </c>
+      <c r="K41">
+        <v>2.1235670241017399E-2</v>
+      </c>
+      <c r="L41">
+        <v>-0.15657687608491999</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>5.1507603606439897E-2</v>
+      </c>
+      <c r="O41">
+        <v>4.8586002273063297E-2</v>
+      </c>
+      <c r="P41">
+        <v>-5.67217484179618E-2</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>2</v>
+      </c>
+      <c r="R41">
+        <v>7.3788929641258702E-2</v>
+      </c>
+      <c r="S41">
+        <v>7.4377708108779E-2</v>
+      </c>
+      <c r="T41">
+        <v>7.9792249377083693E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>104</v>
+      </c>
+      <c r="D42">
+        <v>2016</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>0.110824438622644</v>
+      </c>
+      <c r="G42">
+        <v>0.110824438622644</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>7.8503732957587696E-2</v>
+      </c>
+      <c r="K42">
+        <v>8.0356479363834193E-2</v>
+      </c>
+      <c r="L42">
+        <v>2.3600742747449201E-2</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2</v>
+      </c>
+      <c r="N42">
+        <v>6.9560262669606895E-2</v>
+      </c>
+      <c r="O42">
+        <v>0.120167772524156</v>
+      </c>
+      <c r="P42">
+        <v>0.72753477218626805</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>2</v>
+      </c>
+      <c r="R42">
+        <v>9.22794073904913E-2</v>
+      </c>
+      <c r="S42">
+        <v>0.107859654556362</v>
+      </c>
+      <c r="T42">
+        <v>0.16883774621505299</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>133</v>
+      </c>
+      <c r="D43">
+        <v>4278</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>3.2557962575530099E-2</v>
+      </c>
+      <c r="G43">
+        <v>6.67269920065751E-2</v>
+      </c>
+      <c r="H43">
+        <v>1.04948303665431</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>2.99859287953952E-2</v>
+      </c>
+      <c r="K43">
+        <v>3.2357186441463501E-2</v>
+      </c>
+      <c r="L43">
+        <v>7.9079012767896195E-2</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2</v>
+      </c>
+      <c r="N43">
+        <v>2.9467609779213401E-2</v>
+      </c>
+      <c r="O43">
+        <v>5.7126386360894899E-2</v>
+      </c>
+      <c r="P43">
+        <v>0.93861622265651201</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>7.0844548913511898E-2</v>
+      </c>
+      <c r="S43">
+        <v>7.0844548913511898E-2</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44">
+        <v>12</v>
+      </c>
+      <c r="C44">
+        <v>134</v>
+      </c>
+      <c r="D44">
+        <v>4371</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>1.54011745448941E-2</v>
+      </c>
+      <c r="G44">
+        <v>1.9102950638799E-2</v>
+      </c>
+      <c r="H44">
+        <v>0.24035673922883899</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>1.5241604694849E-2</v>
+      </c>
+      <c r="K44">
+        <v>1.5795565768671901E-2</v>
+      </c>
+      <c r="L44">
+        <v>3.6345324846940703E-2</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2</v>
+      </c>
+      <c r="N44">
+        <v>3.2620122233956397E-2</v>
+      </c>
+      <c r="O44">
+        <v>2.9781466870531698E-2</v>
+      </c>
+      <c r="P44">
+        <v>-8.7021604121084797E-2</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>3</v>
+      </c>
+      <c r="R44">
+        <v>7.1230945123584105E-2</v>
+      </c>
+      <c r="S44">
+        <v>7.2709743474054706E-2</v>
+      </c>
+      <c r="T44">
+        <v>2.0760616722196101E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>143</v>
+      </c>
+      <c r="D45">
+        <v>5253</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>5.9939009761898497E-2</v>
+      </c>
+      <c r="G45">
+        <v>5.9939009761898497E-2</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>2.7856137332038101E-2</v>
+      </c>
+      <c r="K45">
+        <v>6.4402810129334603E-2</v>
+      </c>
+      <c r="L45">
+        <v>1.31197920090892</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2</v>
+      </c>
+      <c r="N45">
+        <v>3.1089941306208901E-2</v>
+      </c>
+      <c r="O45">
+        <v>3.3030276626319903E-2</v>
+      </c>
+      <c r="P45">
+        <v>6.2410388652727501E-2</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>3</v>
+      </c>
+      <c r="R45">
+        <v>5.3586748048751902E-2</v>
+      </c>
+      <c r="S45">
+        <v>5.2449330378479202E-2</v>
+      </c>
+      <c r="T45">
+        <v>-2.1225726727024E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46">
+        <v>12</v>
+      </c>
+      <c r="C46">
+        <v>134</v>
+      </c>
+      <c r="D46">
+        <v>4371</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46">
+        <v>5.8950781605283803E-2</v>
+      </c>
+      <c r="G46">
+        <v>7.8602414817479205E-2</v>
+      </c>
+      <c r="H46">
+        <v>0.33335661847160403</v>
+      </c>
+      <c r="I46" s="1">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>7.3823653542282194E-2</v>
+      </c>
+      <c r="K46">
+        <v>8.4900381713621395E-2</v>
+      </c>
+      <c r="L46">
+        <v>0.15004307752115001</v>
+      </c>
+      <c r="M46" s="1">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>5.8583521771605897E-2</v>
+      </c>
+      <c r="O46">
+        <v>1.6863551460005399E-2</v>
+      </c>
+      <c r="P46">
+        <v>-0.71214513996359297</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>2</v>
+      </c>
+      <c r="R46">
+        <v>4.3208693487408197E-2</v>
+      </c>
+      <c r="S46">
+        <v>4.1654408448964099E-2</v>
+      </c>
+      <c r="T46">
+        <v>-3.5971581480403303E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>134</v>
+      </c>
+      <c r="D47">
+        <v>4371</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+      <c r="F47">
+        <v>0.250888776241456</v>
+      </c>
+      <c r="G47">
+        <v>0.17315441448166499</v>
+      </c>
+      <c r="H47">
+        <v>-0.30983594772282003</v>
+      </c>
+      <c r="I47" s="1">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>9.8807028170468006E-2</v>
+      </c>
+      <c r="K47">
+        <v>9.7234796961639294E-2</v>
+      </c>
+      <c r="L47">
+        <v>-1.59121394291519E-2</v>
+      </c>
+      <c r="M47" s="1">
+        <v>3</v>
+      </c>
+      <c r="N47">
+        <v>0.10372245875441</v>
+      </c>
+      <c r="O47">
+        <v>0.10495691589644</v>
+      </c>
+      <c r="P47">
+        <v>1.1901541448733E-2</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>3</v>
+      </c>
+      <c r="R47">
+        <v>0.10904957851616701</v>
+      </c>
+      <c r="S47">
+        <v>9.7855215867649295E-2</v>
+      </c>
+      <c r="T47">
+        <v>-0.102653882764513</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>134</v>
+      </c>
+      <c r="D48">
+        <v>4371</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <v>0.33644031228430499</v>
+      </c>
+      <c r="G48">
+        <v>0.35124067281525301</v>
+      </c>
+      <c r="H48">
+        <v>4.3991043851012102E-2</v>
+      </c>
+      <c r="I48" s="1">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>0.31467306105557202</v>
+      </c>
+      <c r="K48">
+        <v>0.40983023063797702</v>
+      </c>
+      <c r="L48">
+        <v>0.30240011414767898</v>
+      </c>
+      <c r="M48" s="1">
+        <v>3</v>
+      </c>
+      <c r="N48">
+        <v>0.324576116780674</v>
+      </c>
+      <c r="O48">
+        <v>0.28641046929890102</v>
+      </c>
+      <c r="P48">
+        <v>-0.117586123896981</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>2</v>
+      </c>
+      <c r="R48">
+        <v>0.34913427899079202</v>
+      </c>
+      <c r="S48">
+        <v>0.37419307409264602</v>
+      </c>
+      <c r="T48">
+        <v>7.1774089826665499E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>144</v>
+      </c>
+      <c r="D49">
+        <v>5356</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>8.9143614000139301E-2</v>
+      </c>
+      <c r="G49">
+        <v>9.1604013975246604E-2</v>
+      </c>
+      <c r="H49">
+        <v>2.7600406408286999E-2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>9.4734485650004294E-2</v>
+      </c>
+      <c r="K49">
+        <v>0.130307115454835</v>
+      </c>
+      <c r="L49">
+        <v>0.37549821018983498</v>
+      </c>
+      <c r="M49" s="1">
+        <v>3</v>
+      </c>
+      <c r="N49">
+        <v>8.9327439715184004E-2</v>
+      </c>
+      <c r="O49">
+        <v>8.9428891161403706E-2</v>
+      </c>
+      <c r="P49">
+        <v>1.1357254449824901E-3</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>3</v>
+      </c>
+      <c r="R49">
+        <v>7.0503557488901705E-2</v>
+      </c>
+      <c r="S49">
+        <v>6.98860967078309E-2</v>
+      </c>
+      <c r="T49">
+        <v>-8.7578670220719301E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>144</v>
+      </c>
+      <c r="D50">
+        <v>5356</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50">
+        <v>9.41217925513603E-2</v>
+      </c>
+      <c r="G50">
+        <v>8.9863945243907006E-2</v>
+      </c>
+      <c r="H50">
+        <v>-4.5237635111229899E-2</v>
+      </c>
+      <c r="I50" s="1">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>0.10743043017020799</v>
+      </c>
+      <c r="K50">
+        <v>8.1164025334700102E-2</v>
+      </c>
+      <c r="L50">
+        <v>-0.24449687852773899</v>
+      </c>
+      <c r="M50" s="1">
+        <v>3</v>
+      </c>
+      <c r="N50">
+        <v>0.10600926084781</v>
+      </c>
+      <c r="O50">
+        <v>8.4007018737823902E-2</v>
+      </c>
+      <c r="P50">
+        <v>-0.20755018886107701</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>3</v>
+      </c>
+      <c r="R50">
+        <v>8.9358015705435195E-2</v>
+      </c>
+      <c r="S50">
+        <v>0.10347239466543801</v>
+      </c>
+      <c r="T50">
+        <v>0.15795313770764999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>144</v>
+      </c>
+      <c r="D51">
+        <v>5356</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>0.255197115132833</v>
+      </c>
+      <c r="G51">
+        <v>0.270351519117215</v>
+      </c>
+      <c r="H51">
+        <v>5.9383132040868002E-2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>0.22915142307699901</v>
+      </c>
+      <c r="K51">
+        <v>0.24248933926772301</v>
+      </c>
+      <c r="L51">
+        <v>5.8205687800776298E-2</v>
+      </c>
+      <c r="M51" s="1">
+        <v>2</v>
+      </c>
+      <c r="N51">
+        <v>0.231929361740353</v>
+      </c>
+      <c r="O51">
+        <v>0.243562764402629</v>
+      </c>
+      <c r="P51">
+        <v>5.0159249242874702E-2</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>3</v>
+      </c>
+      <c r="R51">
+        <v>0.26807303863787901</v>
+      </c>
+      <c r="S51">
+        <v>0.274680159123946</v>
+      </c>
+      <c r="T51">
+        <v>2.46467176245663E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>132</v>
+      </c>
+      <c r="D52">
+        <v>4186</v>
+      </c>
+      <c r="E52" s="1">
+        <v>3</v>
+      </c>
+      <c r="F52">
+        <v>8.1368953390957899E-2</v>
+      </c>
+      <c r="G52">
+        <v>0.119677273462969</v>
+      </c>
+      <c r="H52">
+        <v>0.47079774871811098</v>
+      </c>
+      <c r="I52" s="1">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>5.91558153101693E-2</v>
+      </c>
+      <c r="K52">
+        <v>5.4468513254757399E-2</v>
+      </c>
+      <c r="L52">
+        <v>-7.9236538805782603E-2</v>
+      </c>
+      <c r="M52" s="1">
+        <v>3</v>
+      </c>
+      <c r="N52">
+        <v>7.2474880946372694E-2</v>
+      </c>
+      <c r="O52">
+        <v>7.1167412581100403E-2</v>
+      </c>
+      <c r="P52">
+        <v>-1.8040296833874599E-2</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>2</v>
+      </c>
+      <c r="R52">
+        <v>0.12262561898798401</v>
+      </c>
+      <c r="S52">
+        <v>0.12140496409319</v>
+      </c>
+      <c r="T52">
+        <v>-9.9543219831807802E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53">
+        <v>12</v>
+      </c>
+      <c r="C53">
+        <v>108</v>
+      </c>
+      <c r="D53">
+        <v>2278</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53">
+        <v>4.9201959354256898E-2</v>
+      </c>
+      <c r="G53">
+        <v>4.3263098628202802E-2</v>
+      </c>
+      <c r="H53">
+        <v>-0.12070374440363101</v>
+      </c>
+      <c r="I53" s="1">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>5.8791282129130297E-2</v>
+      </c>
+      <c r="K53">
+        <v>3.5587327398551E-2</v>
+      </c>
+      <c r="L53">
+        <v>-0.39468359746966702</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2</v>
+      </c>
+      <c r="N53">
+        <v>4.1692731018111301E-2</v>
+      </c>
+      <c r="O53">
+        <v>4.4948638230637397E-2</v>
+      </c>
+      <c r="P53">
+        <v>7.8092922507566803E-2</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>2</v>
+      </c>
+      <c r="R53">
+        <v>4.1412569870740899E-2</v>
+      </c>
+      <c r="S53">
+        <v>4.1932195293614097E-2</v>
+      </c>
+      <c r="T53">
+        <v>1.2547529035148801E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>134</v>
+      </c>
+      <c r="D54">
+        <v>4371</v>
+      </c>
+      <c r="E54" s="1">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>0.22095759948732599</v>
+      </c>
+      <c r="G54">
+        <v>0.12607300347554001</v>
+      </c>
+      <c r="H54">
+        <v>-0.42942445171354299</v>
+      </c>
+      <c r="I54" s="1">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>0.16537776836930301</v>
+      </c>
+      <c r="K54">
+        <v>0.14569081288663399</v>
+      </c>
+      <c r="L54">
+        <v>-0.11904233366304701</v>
+      </c>
+      <c r="M54" s="1">
+        <v>3</v>
+      </c>
+      <c r="N54">
+        <v>0.180637246894752</v>
+      </c>
+      <c r="O54">
+        <v>0.13507396272272501</v>
+      </c>
+      <c r="P54">
+        <v>-0.25223637403294502</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>3</v>
+      </c>
+      <c r="R54">
+        <v>0.185138840881612</v>
+      </c>
+      <c r="S54">
+        <v>0.17177589579869201</v>
+      </c>
+      <c r="T54">
+        <v>-7.2177966650796899E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>134</v>
+      </c>
+      <c r="D55">
+        <v>4371</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+      <c r="F55">
+        <v>0.293246938649384</v>
+      </c>
+      <c r="G55">
+        <v>0.29734342076692399</v>
+      </c>
+      <c r="H55">
+        <v>1.3969394314591E-2</v>
+      </c>
+      <c r="I55" s="1">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>9.8788598213413598E-2</v>
+      </c>
+      <c r="K55">
+        <v>9.7758002354330603E-2</v>
+      </c>
+      <c r="L55">
+        <v>-1.04323360966877E-2</v>
+      </c>
+      <c r="M55" s="1">
+        <v>3</v>
+      </c>
+      <c r="N55">
+        <v>0.121442354452301</v>
+      </c>
+      <c r="O55">
+        <v>0.12568098092951599</v>
+      </c>
+      <c r="P55">
+        <v>3.4902374022072698E-2</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>3</v>
+      </c>
+      <c r="R55">
+        <v>0.16775894784176501</v>
+      </c>
+      <c r="S55">
+        <v>0.18702109295006</v>
+      </c>
+      <c r="T55">
+        <v>0.114820373852502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>134</v>
+      </c>
+      <c r="D56">
+        <v>4371</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>0.13176092032359699</v>
+      </c>
+      <c r="G56">
+        <v>0.19640786998747101</v>
+      </c>
+      <c r="H56">
+        <v>0.49063826744002798</v>
+      </c>
+      <c r="I56" s="1">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>8.5930028429650807E-2</v>
+      </c>
+      <c r="K56">
+        <v>5.8503875387216901E-2</v>
+      </c>
+      <c r="L56">
+        <v>-0.31916843906187098</v>
+      </c>
+      <c r="M56" s="1">
+        <v>3</v>
+      </c>
+      <c r="N56">
+        <v>0.108550948878516</v>
+      </c>
+      <c r="O56">
+        <v>0.120515398870716</v>
+      </c>
+      <c r="P56">
+        <v>0.11021967210613499</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>3</v>
+      </c>
+      <c r="R56">
+        <v>0.13456957649661999</v>
+      </c>
+      <c r="S56">
+        <v>0.12648509122684301</v>
+      </c>
+      <c r="T56">
+        <v>-6.0076619695536099E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>126</v>
+      </c>
+      <c r="D57">
+        <v>3655</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57">
+        <v>0.19895435899823499</v>
+      </c>
+      <c r="G57">
+        <v>0.15619202963024501</v>
+      </c>
+      <c r="H57">
+        <v>-0.21493537303381999</v>
+      </c>
+      <c r="I57" s="1">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>0.122408603319955</v>
+      </c>
+      <c r="K57">
+        <v>0.11947802606459</v>
+      </c>
+      <c r="L57">
+        <v>-2.3940941860966E-2</v>
+      </c>
+      <c r="M57" s="1">
+        <v>2</v>
+      </c>
+      <c r="N57">
+        <v>0.12555699966908199</v>
+      </c>
+      <c r="O57">
+        <v>0.12182053583244799</v>
+      </c>
+      <c r="P57">
+        <v>-2.9759104203516299E-2</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>0.14506941908151599</v>
+      </c>
+      <c r="S57">
+        <v>0.141186609215153</v>
+      </c>
+      <c r="T57">
+        <v>-2.6765185184764902E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>126</v>
+      </c>
+      <c r="D58">
+        <v>3655</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>0.16391567610653199</v>
+      </c>
+      <c r="G58">
+        <v>9.8419971514746504E-2</v>
+      </c>
+      <c r="H58">
+        <v>-0.39956949907108602</v>
+      </c>
+      <c r="I58" s="1">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>8.8243017792479797E-2</v>
+      </c>
+      <c r="K58">
+        <v>8.8243017792479797E-2</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>7.5913489891626496E-2</v>
+      </c>
+      <c r="O58">
+        <v>7.5913489891626496E-2</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <v>6.8032962357341395E-2</v>
+      </c>
+      <c r="S58">
+        <v>6.8032962357341395E-2</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>126</v>
+      </c>
+      <c r="D59">
+        <v>3655</v>
+      </c>
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+      <c r="F59">
+        <v>8.6804146479806596E-2</v>
+      </c>
+      <c r="G59">
+        <v>0.114712604085815</v>
+      </c>
+      <c r="H59">
+        <v>0.32151065055977901</v>
+      </c>
+      <c r="I59" s="1">
+        <v>3</v>
+      </c>
+      <c r="J59">
+        <v>0.13541584116614699</v>
+      </c>
+      <c r="K59">
+        <v>9.0778803458263793E-2</v>
+      </c>
+      <c r="L59">
+        <v>-0.32962936480316601</v>
+      </c>
+      <c r="M59" s="1">
+        <v>3</v>
+      </c>
+      <c r="N59">
+        <v>0.11371280760694</v>
+      </c>
+      <c r="O59">
+        <v>9.4603772891344001E-2</v>
+      </c>
+      <c r="P59">
+        <v>-0.16804645947753799</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>3</v>
+      </c>
+      <c r="R59">
+        <v>0.13592409955363</v>
+      </c>
+      <c r="S59">
+        <v>0.14762747839340801</v>
+      </c>
+      <c r="T59">
+        <v>8.6102309143200106E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60">
+        <v>12</v>
+      </c>
+      <c r="C60">
+        <v>126</v>
+      </c>
+      <c r="D60">
+        <v>3655</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>0.21282963894565399</v>
+      </c>
+      <c r="G60">
+        <v>5.0379951471666198E-2</v>
+      </c>
+      <c r="H60">
+        <v>-0.76328507758014497</v>
+      </c>
+      <c r="I60" s="1">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>2.942307959963E-2</v>
+      </c>
+      <c r="K60">
+        <v>2.942307959963E-2</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>2.42510512565745E-2</v>
+      </c>
+      <c r="O60">
+        <v>2.42510512565745E-2</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>1</v>
+      </c>
+      <c r="R60">
+        <v>4.4268851825128901E-2</v>
+      </c>
+      <c r="S60">
+        <v>4.4268851825128901E-2</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61">
+        <v>12</v>
+      </c>
+      <c r="C61">
+        <v>126</v>
+      </c>
+      <c r="D61">
+        <v>3655</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>9.2912459788391896E-2</v>
+      </c>
+      <c r="G61">
+        <v>4.8901542435072998E-2</v>
+      </c>
+      <c r="H61">
+        <v>-0.47368154339637097</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>4.9491499722273499E-2</v>
+      </c>
+      <c r="K61">
+        <v>5.4292690360484099E-2</v>
+      </c>
+      <c r="L61">
+        <v>9.7010409164259306E-2</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>4.9680660077020301E-2</v>
+      </c>
+      <c r="O61">
+        <v>4.9680660077020301E-2</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>1</v>
+      </c>
+      <c r="R61">
+        <v>5.5834655147909397E-2</v>
+      </c>
+      <c r="S61">
+        <v>5.5834655147909397E-2</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62">
+        <v>12</v>
+      </c>
+      <c r="C62">
+        <v>120</v>
+      </c>
+      <c r="D62">
+        <v>3160</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>0.161612973343495</v>
+      </c>
+      <c r="G62">
+        <v>0.15224505351113499</v>
+      </c>
+      <c r="H62">
+        <v>-5.7965147466529601E-2</v>
+      </c>
+      <c r="I62" s="1">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>0.133859272527108</v>
+      </c>
+      <c r="K62">
+        <v>0.14190060971144799</v>
+      </c>
+      <c r="L62">
+        <v>6.0073068025315202E-2</v>
+      </c>
+      <c r="M62" s="1">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>0.13166601151985599</v>
+      </c>
+      <c r="O62">
+        <v>0.116594868178639</v>
+      </c>
+      <c r="P62">
+        <v>-0.114464949361242</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>2</v>
+      </c>
+      <c r="R62">
+        <v>0.16499734127909199</v>
+      </c>
+      <c r="S62">
+        <v>0.14287952014750799</v>
+      </c>
+      <c r="T62">
+        <v>-0.13404956079972</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>120</v>
+      </c>
+      <c r="D63">
+        <v>3160</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+      <c r="F63">
+        <v>0.19568586333375801</v>
+      </c>
+      <c r="G63">
+        <v>0.190422390536993</v>
+      </c>
+      <c r="H63">
+        <v>-2.6897562793218099E-2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>0.18015113972694399</v>
+      </c>
+      <c r="K63">
+        <v>0.18015113972694399</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>0.17745921265064701</v>
+      </c>
+      <c r="O63">
+        <v>0.17745921265064701</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <v>0.16609708243943599</v>
+      </c>
+      <c r="S63">
+        <v>0.16609708243943599</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>78</v>
+      </c>
+      <c r="H65">
+        <f>AVERAGE(H37:H63)</f>
+        <v>4.9011408614199566E-2</v>
+      </c>
+      <c r="L65">
+        <f>AVERAGE(L37:L63)</f>
+        <v>3.2000463578012055E-2</v>
+      </c>
+      <c r="P65">
+        <f>AVERAGE(P37:P63)</f>
+        <v>-1.4585573865395161E-2</v>
+      </c>
+      <c r="T65">
+        <f>AVERAGE(T37:T63)</f>
+        <v>-8.8891640826889232E-3</v>
       </c>
     </row>
   </sheetData>

--- a/forecast/data/results_12.xlsx
+++ b/forecast/data/results_12.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\segmentation\forecast\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CC116C3-6628-4F15-8CB7-8BD2B32D87B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B857BE-80F7-4EE8-BEC3-57A93AB3D07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="270" windowWidth="15300" windowHeight="9960" xr2:uid="{F88E971C-6354-4E44-8263-82A7DCD4B89A}"/>
+    <workbookView xWindow="1476" yWindow="684" windowWidth="20388" windowHeight="13644" xr2:uid="{F88E971C-6354-4E44-8263-82A7DCD4B89A}"/>
   </bookViews>
   <sheets>
     <sheet name="results_12" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -263,6 +279,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -749,9 +768,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1128,15 +1148,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5253919-043D-4941-80FA-5BD2C3713B39}">
   <dimension ref="A2:T65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="5" max="5" width="9.109375" style="1"/>
+    <col min="9" max="9" width="9.109375" style="1"/>
+    <col min="13" max="13" width="9.109375" style="1"/>
+    <col min="17" max="17" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1198,7 +1218,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1220,7 +1240,7 @@
       <c r="G3">
         <v>0.15966381270021099</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>-0.130407105561858</v>
       </c>
       <c r="I3" s="1">
@@ -1256,11 +1276,11 @@
       <c r="S3">
         <v>0.28857855429208001</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="2">
         <v>0.47328342573694399</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1282,7 +1302,7 @@
       <c r="G4">
         <v>4.1557988610444997E-2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>0.12954251048826901</v>
       </c>
       <c r="I4" s="1">
@@ -1318,11 +1338,11 @@
       <c r="S4">
         <v>5.1165590740838499E-2</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="2">
         <v>2.8186482694956799E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1344,7 +1364,7 @@
       <c r="G5">
         <v>7.7099348675065904E-2</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>-0.111554447982537</v>
       </c>
       <c r="I5" s="1">
@@ -1380,11 +1400,11 @@
       <c r="S5">
         <v>9.9227187669380698E-2</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="2">
         <v>5.1946252996974203E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1406,7 +1426,7 @@
       <c r="G6">
         <v>7.4182462834923593E-2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>1.2969393111122199E-2</v>
       </c>
       <c r="I6" s="1">
@@ -1442,11 +1462,11 @@
       <c r="S6">
         <v>7.9337148218791995E-2</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="2">
         <v>4.2367573982881303E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1468,7 +1488,7 @@
       <c r="G7">
         <v>2.3651722483407401E-2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>0.45755952442741799</v>
       </c>
       <c r="I7" s="1">
@@ -1504,11 +1524,11 @@
       <c r="S7">
         <v>7.74204346364325E-2</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="2">
         <v>3.51555410219849</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1530,7 +1550,7 @@
       <c r="G8">
         <v>0.22563826205476101</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>5.1538317781998604</v>
       </c>
       <c r="I8" s="1">
@@ -1566,11 +1586,11 @@
       <c r="S8">
         <v>4.3748675825106199E-2</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="2">
         <v>-0.57133460120778101</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1592,7 +1612,7 @@
       <c r="G9">
         <v>3.8376902277081001E-2</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>-0.56661822630318004</v>
       </c>
       <c r="I9" s="1">
@@ -1628,11 +1648,11 @@
       <c r="S9">
         <v>3.1850858129023198E-2</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="2">
         <v>2.3832690437275601E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1654,7 +1674,7 @@
       <c r="G10">
         <v>0.46110917905870702</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>0.112680826832311</v>
       </c>
       <c r="I10" s="1">
@@ -1690,11 +1710,11 @@
       <c r="S10">
         <v>0.51460218939279201</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1716,7 +1736,7 @@
       <c r="G11">
         <v>2.9712963068275099E-2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>0.60400764946735597</v>
       </c>
       <c r="I11" s="1">
@@ -1752,11 +1772,11 @@
       <c r="S11">
         <v>7.9363447037885906E-2</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="2">
         <v>-1.0153493988691E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1778,7 +1798,7 @@
       <c r="G12">
         <v>0.92519948111737305</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>1.8002888544511699</v>
       </c>
       <c r="I12" s="1">
@@ -1814,11 +1834,11 @@
       <c r="S12">
         <v>5.9354646714509997E-2</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="2">
         <v>-6.1472443439396099E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1840,7 +1860,7 @@
       <c r="G13">
         <v>4.1014660410022101E-2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>-9.9332748830413903E-2</v>
       </c>
       <c r="I13" s="1">
@@ -1876,11 +1896,11 @@
       <c r="S13">
         <v>4.2165521064128998E-2</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="2">
         <v>-2.7798930935120199E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1902,7 +1922,7 @@
       <c r="G14">
         <v>0.171607616323871</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>0.28016585850925901</v>
       </c>
       <c r="I14" s="1">
@@ -1938,11 +1958,11 @@
       <c r="S14">
         <v>0.18935231090506699</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="2">
         <v>-5.4027842543352897E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1964,7 +1984,7 @@
       <c r="G15">
         <v>0.170136533995393</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>-1.4385312224763899E-2</v>
       </c>
       <c r="I15" s="1">
@@ -2000,11 +2020,11 @@
       <c r="S15">
         <v>0.16323258264533599</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="2">
         <v>-3.2173527188145902E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -2026,7 +2046,7 @@
       <c r="G16">
         <v>0.24688627224322299</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>-0.10540709318790401</v>
       </c>
       <c r="I16" s="1">
@@ -2062,11 +2082,11 @@
       <c r="S16">
         <v>0.206927973113676</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="2">
         <v>-1.5337626400170499E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2088,7 +2108,7 @@
       <c r="G17">
         <v>0.21977320714922799</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>0.457263422931246</v>
       </c>
       <c r="I17" s="1">
@@ -2124,11 +2144,11 @@
       <c r="S17">
         <v>0.149371369668237</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="2">
         <v>-0.20920475987270701</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -2150,7 +2170,7 @@
       <c r="G18">
         <v>6.4931622869492403E-2</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>-0.412802158671421</v>
       </c>
       <c r="I18" s="1">
@@ -2186,11 +2206,11 @@
       <c r="S18">
         <v>7.7694498375169799E-2</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="2">
         <v>-6.6078891637822199E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -2212,7 +2232,7 @@
       <c r="G19">
         <v>4.2226070165471703E-2</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>0.92321387034876301</v>
       </c>
       <c r="I19" s="1">
@@ -2248,11 +2268,11 @@
       <c r="S19">
         <v>0.138362426655607</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="2">
         <v>-9.5853170887709397E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -2274,7 +2294,7 @@
       <c r="G20">
         <v>8.1580100583596604E-2</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>-0.47882873874845699</v>
       </c>
       <c r="I20" s="1">
@@ -2310,11 +2330,11 @@
       <c r="S20">
         <v>0.18638845306021601</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="2">
         <v>6.4746526508515603E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -2336,7 +2356,7 @@
       <c r="G21">
         <v>0.13878682435547601</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>-2.1577900847792601E-2</v>
       </c>
       <c r="I21" s="1">
@@ -2372,11 +2392,11 @@
       <c r="S21">
         <v>0.12693722774902799</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="2">
         <v>-2.5158521197481701E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2398,7 +2418,7 @@
       <c r="G22">
         <v>0.197912348503858</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>-0.19062656683065399</v>
       </c>
       <c r="I22" s="1">
@@ -2434,11 +2454,11 @@
       <c r="S22">
         <v>0.236197038486615</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="2">
         <v>6.0292699246725097E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2460,7 +2480,7 @@
       <c r="G23">
         <v>0.15858262715093099</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>-0.28604441544102899</v>
       </c>
       <c r="I23" s="1">
@@ -2496,11 +2516,11 @@
       <c r="S23">
         <v>0.13731333810260499</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="2">
         <v>-9.3450255392244996E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -2522,7 +2542,7 @@
       <c r="G24">
         <v>0.14508086239187001</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>-0.109591357076663</v>
       </c>
       <c r="I24" s="1">
@@ -2558,11 +2578,11 @@
       <c r="S24">
         <v>0.19054641988516</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="2">
         <v>4.4493060660726398E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -2584,7 +2604,7 @@
       <c r="G25">
         <v>5.1346711728193599E-2</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>0</v>
       </c>
       <c r="I25" s="1">
@@ -2620,11 +2640,11 @@
       <c r="S25">
         <v>0.113802556245182</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="2">
         <v>4.5378039269370798E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -2646,7 +2666,7 @@
       <c r="G26">
         <v>0.28164250417645098</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>0.30586675510025502</v>
       </c>
       <c r="I26" s="1">
@@ -2682,11 +2702,11 @@
       <c r="S26">
         <v>0.196392495295936</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="2">
         <v>-5.6022495071492602E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -2708,7 +2728,7 @@
       <c r="G27">
         <v>0.119695802964065</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>0.43541064271188601</v>
       </c>
       <c r="I27" s="1">
@@ -2744,11 +2764,11 @@
       <c r="S27">
         <v>0.20249510928938899</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -2770,7 +2790,7 @@
       <c r="G28">
         <v>0.137125324217485</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>-0.208056795486216</v>
       </c>
       <c r="I28" s="1">
@@ -2806,11 +2826,11 @@
       <c r="S28">
         <v>5.2994551251880601E-2</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="2">
         <v>-8.3022603910255094E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2832,7 +2852,7 @@
       <c r="G29">
         <v>3.5025219800764902E-2</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>-0.55841825705500203</v>
       </c>
       <c r="I29" s="1">
@@ -2868,11 +2888,11 @@
       <c r="S29">
         <v>0.122438058940729</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="2">
         <v>2.42427411843388E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2894,7 +2914,7 @@
       <c r="G30">
         <v>0.13087662123069699</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="2">
         <v>0.30866060862667999</v>
       </c>
       <c r="I30" s="1">
@@ -2930,11 +2950,11 @@
       <c r="S30">
         <v>0.16776856679206201</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="2">
         <v>6.9234559515804301</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2956,7 +2976,7 @@
       <c r="G31">
         <v>0.22129449978768601</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>0.261361363002311</v>
       </c>
       <c r="I31" s="1">
@@ -2992,11 +3012,11 @@
       <c r="S31">
         <v>0.12711973826258</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="2">
         <v>3.3486269804346699E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -3018,7 +3038,7 @@
       <c r="G32">
         <v>3.2298623277332697E-2</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>-0.71937294304935295</v>
       </c>
       <c r="I32" s="1">
@@ -3054,11 +3074,11 @@
       <c r="S32">
         <v>7.9215690939714506E-2</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="2">
         <v>-1.6547052191855701E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -3079,7 +3099,7 @@
         <v>0.33535266077205689</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -3125,7 +3145,7 @@
       <c r="O37">
         <v>4.6173398969424101E-2</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="2">
         <v>0.23440584708901299</v>
       </c>
       <c r="Q37" s="1">
@@ -3137,11 +3157,11 @@
       <c r="S37">
         <v>6.3321785349017806E-2</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3187,7 +3207,7 @@
       <c r="O38">
         <v>3.3211135161410499E-2</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="2">
         <v>-0.29501627122975199</v>
       </c>
       <c r="Q38" s="1">
@@ -3199,11 +3219,11 @@
       <c r="S38">
         <v>2.4569276504240602E-2</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="2">
         <v>-0.612617546569734</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3249,7 +3269,7 @@
       <c r="O39">
         <v>7.5752218812966496E-2</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="2">
         <v>-0.156394435245089</v>
       </c>
       <c r="Q39" s="1">
@@ -3261,11 +3281,11 @@
       <c r="S39">
         <v>0.123242248426843</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="2">
         <v>-1.5809210606316199E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -3311,7 +3331,7 @@
       <c r="O40">
         <v>8.3227146476201205E-2</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="2">
         <v>-0.4282065140779</v>
       </c>
       <c r="Q40" s="1">
@@ -3323,11 +3343,11 @@
       <c r="S40">
         <v>0.168365196803482</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="2">
         <v>0.19463029418677</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -3373,7 +3393,7 @@
       <c r="O41">
         <v>4.8586002273063297E-2</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="2">
         <v>-5.67217484179618E-2</v>
       </c>
       <c r="Q41" s="1">
@@ -3385,11 +3405,11 @@
       <c r="S41">
         <v>7.4377708108779E-2</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="2">
         <v>7.9792249377083693E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>55</v>
       </c>
@@ -3435,7 +3455,7 @@
       <c r="O42">
         <v>0.120167772524156</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="2">
         <v>0.72753477218626805</v>
       </c>
       <c r="Q42" s="1">
@@ -3447,11 +3467,11 @@
       <c r="S42">
         <v>0.107859654556362</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="2">
         <v>0.16883774621505299</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>56</v>
       </c>
@@ -3497,7 +3517,7 @@
       <c r="O43">
         <v>5.7126386360894899E-2</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="2">
         <v>0.93861622265651201</v>
       </c>
       <c r="Q43" s="1">
@@ -3509,11 +3529,11 @@
       <c r="S43">
         <v>7.0844548913511898E-2</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -3559,7 +3579,7 @@
       <c r="O44">
         <v>2.9781466870531698E-2</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="2">
         <v>-8.7021604121084797E-2</v>
       </c>
       <c r="Q44" s="1">
@@ -3571,11 +3591,11 @@
       <c r="S44">
         <v>7.2709743474054706E-2</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="2">
         <v>2.0760616722196101E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>58</v>
       </c>
@@ -3621,7 +3641,7 @@
       <c r="O45">
         <v>3.3030276626319903E-2</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="2">
         <v>6.2410388652727501E-2</v>
       </c>
       <c r="Q45" s="1">
@@ -3633,11 +3653,11 @@
       <c r="S45">
         <v>5.2449330378479202E-2</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="2">
         <v>-2.1225726727024E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -3683,7 +3703,7 @@
       <c r="O46">
         <v>1.6863551460005399E-2</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="2">
         <v>-0.71214513996359297</v>
       </c>
       <c r="Q46" s="1">
@@ -3695,11 +3715,11 @@
       <c r="S46">
         <v>4.1654408448964099E-2</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="2">
         <v>-3.5971581480403303E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>60</v>
       </c>
@@ -3745,7 +3765,7 @@
       <c r="O47">
         <v>0.10495691589644</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="2">
         <v>1.1901541448733E-2</v>
       </c>
       <c r="Q47" s="1">
@@ -3757,11 +3777,11 @@
       <c r="S47">
         <v>9.7855215867649295E-2</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="2">
         <v>-0.102653882764513</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3807,7 +3827,7 @@
       <c r="O48">
         <v>0.28641046929890102</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="2">
         <v>-0.117586123896981</v>
       </c>
       <c r="Q48" s="1">
@@ -3819,11 +3839,11 @@
       <c r="S48">
         <v>0.37419307409264602</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="2">
         <v>7.1774089826665499E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>62</v>
       </c>
@@ -3869,7 +3889,7 @@
       <c r="O49">
         <v>8.9428891161403706E-2</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="2">
         <v>1.1357254449824901E-3</v>
       </c>
       <c r="Q49" s="1">
@@ -3881,11 +3901,11 @@
       <c r="S49">
         <v>6.98860967078309E-2</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="2">
         <v>-8.7578670220719301E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3931,7 +3951,7 @@
       <c r="O50">
         <v>8.4007018737823902E-2</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="2">
         <v>-0.20755018886107701</v>
       </c>
       <c r="Q50" s="1">
@@ -3943,11 +3963,11 @@
       <c r="S50">
         <v>0.10347239466543801</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="2">
         <v>0.15795313770764999</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -3993,7 +4013,7 @@
       <c r="O51">
         <v>0.243562764402629</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="2">
         <v>5.0159249242874702E-2</v>
       </c>
       <c r="Q51" s="1">
@@ -4005,11 +4025,11 @@
       <c r="S51">
         <v>0.274680159123946</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="2">
         <v>2.46467176245663E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>65</v>
       </c>
@@ -4055,7 +4075,7 @@
       <c r="O52">
         <v>7.1167412581100403E-2</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="2">
         <v>-1.8040296833874599E-2</v>
       </c>
       <c r="Q52" s="1">
@@ -4067,11 +4087,11 @@
       <c r="S52">
         <v>0.12140496409319</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="2">
         <v>-9.9543219831807802E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -4117,7 +4137,7 @@
       <c r="O53">
         <v>4.4948638230637397E-2</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="2">
         <v>7.8092922507566803E-2</v>
       </c>
       <c r="Q53" s="1">
@@ -4129,11 +4149,11 @@
       <c r="S53">
         <v>4.1932195293614097E-2</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="2">
         <v>1.2547529035148801E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -4179,7 +4199,7 @@
       <c r="O54">
         <v>0.13507396272272501</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="2">
         <v>-0.25223637403294502</v>
       </c>
       <c r="Q54" s="1">
@@ -4191,11 +4211,11 @@
       <c r="S54">
         <v>0.17177589579869201</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="2">
         <v>-7.2177966650796899E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>68</v>
       </c>
@@ -4241,7 +4261,7 @@
       <c r="O55">
         <v>0.12568098092951599</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="2">
         <v>3.4902374022072698E-2</v>
       </c>
       <c r="Q55" s="1">
@@ -4253,11 +4273,11 @@
       <c r="S55">
         <v>0.18702109295006</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="2">
         <v>0.114820373852502</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -4303,7 +4323,7 @@
       <c r="O56">
         <v>0.120515398870716</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="2">
         <v>0.11021967210613499</v>
       </c>
       <c r="Q56" s="1">
@@ -4315,11 +4335,11 @@
       <c r="S56">
         <v>0.12648509122684301</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="2">
         <v>-6.0076619695536099E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -4365,7 +4385,7 @@
       <c r="O57">
         <v>0.12182053583244799</v>
       </c>
-      <c r="P57">
+      <c r="P57" s="2">
         <v>-2.9759104203516299E-2</v>
       </c>
       <c r="Q57" s="1">
@@ -4377,11 +4397,11 @@
       <c r="S57">
         <v>0.141186609215153</v>
       </c>
-      <c r="T57">
+      <c r="T57" s="2">
         <v>-2.6765185184764902E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>71</v>
       </c>
@@ -4427,7 +4447,7 @@
       <c r="O58">
         <v>7.5913489891626496E-2</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="2">
         <v>0</v>
       </c>
       <c r="Q58" s="1">
@@ -4439,11 +4459,11 @@
       <c r="S58">
         <v>6.8032962357341395E-2</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -4489,7 +4509,7 @@
       <c r="O59">
         <v>9.4603772891344001E-2</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="2">
         <v>-0.16804645947753799</v>
       </c>
       <c r="Q59" s="1">
@@ -4501,11 +4521,11 @@
       <c r="S59">
         <v>0.14762747839340801</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="2">
         <v>8.6102309143200106E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -4551,7 +4571,7 @@
       <c r="O60">
         <v>2.42510512565745E-2</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="2">
         <v>0</v>
       </c>
       <c r="Q60" s="1">
@@ -4563,11 +4583,11 @@
       <c r="S60">
         <v>4.4268851825128901E-2</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -4613,7 +4633,7 @@
       <c r="O61">
         <v>4.9680660077020301E-2</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="2">
         <v>0</v>
       </c>
       <c r="Q61" s="1">
@@ -4625,11 +4645,11 @@
       <c r="S61">
         <v>5.5834655147909397E-2</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -4675,7 +4695,7 @@
       <c r="O62">
         <v>0.116594868178639</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="2">
         <v>-0.114464949361242</v>
       </c>
       <c r="Q62" s="1">
@@ -4687,11 +4707,11 @@
       <c r="S62">
         <v>0.14287952014750799</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="2">
         <v>-0.13404956079972</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -4737,7 +4757,7 @@
       <c r="O63">
         <v>0.17745921265064701</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="2">
         <v>0</v>
       </c>
       <c r="Q63" s="1">
@@ -4749,11 +4769,11 @@
       <c r="S63">
         <v>0.16609708243943599</v>
       </c>
-      <c r="T63">
+      <c r="T63" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>78</v>
       </c>
